--- a/docs/exports/division/Division_H.xlsx
+++ b/docs/exports/division/Division_H.xlsx
@@ -1,17 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Division H — Level Totals (D" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Area Leaderboard (within Div" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Club Leaderboard (within Div" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pathways Quality Award — Exc" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pathways Quality Award — Sta" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Division H — Level Totals (D" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="District-Wide Standing — Ran" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Area Leaderboard (within Div" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Club Leaderboard (within Div" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Pathways Quality Award — Exc" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Pathways Quality Award — Sta" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -580,6 +581,106 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>District 82 — Division H Director Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Pathways Education Performance — Division H</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Snapshot as of 2026-06-30  |  District 82 Toastmasters Pathways Dashboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>District-Wide Standing — Rank Among All Divisions</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Level 1 Rank</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Level 2 Rank</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Level 3 Rank</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Level 4+ Rank</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Total Levels Rank</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Out of 9 divisions in the district.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -780,7 +881,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1444,13 +1545,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1458,8 +1559,7 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1518,11 +1618,6 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Qualifying Date</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
           <t>Ovation 2027</t>
         </is>
       </c>
@@ -1549,11 +1644,6 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
           <t>Yes</t>
         </is>
       </c>
@@ -1578,12 +1668,7 @@
       <c r="E8" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr"/>
+      <c r="F8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
@@ -1605,12 +1690,7 @@
       <c r="E9" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -1632,25 +1712,20 @@
       <c r="E10" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr"/>
+      <c r="F10" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1658,8 +1733,6 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1716,12 +1789,6 @@
           <t>Level 3</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Qualifying Date</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
@@ -1743,12 +1810,6 @@
       <c r="E7" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -1770,12 +1831,6 @@
       <c r="E8" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
@@ -1797,12 +1852,6 @@
       <c r="E9" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -1824,12 +1873,6 @@
       <c r="E10" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
@@ -1851,12 +1894,6 @@
       <c r="E11" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/exports/division/Division_H.xlsx
+++ b/docs/exports/division/Division_H.xlsx
@@ -11,8 +11,8 @@
     <sheet name="District-Wide Standing — Ran" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Area Leaderboard (within Div" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Club Leaderboard (within Div" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Pathways Quality Award — Exc" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Pathways Quality Award — Sta" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Clubs Qualifying — Excellenc" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Clubs Qualifying — Star (thi" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-06-30  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:26  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-06-30  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:26  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-06-30  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:26  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -917,7 +917,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-06-30  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:26  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1036,25 +1036,25 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Wattala Toastmasters Club</t>
+          <t>Ja-Ela Toastmasters Club</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>3</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>18</v>
@@ -1066,25 +1066,25 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Ja-Ela Toastmasters Club</t>
+          <t>Wattala Toastmasters Club</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F10" s="8" t="n">
         <v>3</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H10" s="8" t="n">
         <v>18</v>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Star Garments Toastmasters Club</t>
+          <t>Minuwangoda Toastmasters Club</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>SriLankan Airlines Toastmasters Club</t>
+          <t>Ragama Toastmasters Club</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Minuwangoda Toastmasters Club</t>
+          <t>SriLankan Airlines Toastmasters Club</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Ragama Toastmasters Club</t>
+          <t>Star Garments Toastmasters Club</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
@@ -1426,12 +1426,12 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>IAB Toastmasters Club</t>
+          <t>Ansell Textiles Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>04</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Wennappuwa Toastmasters Club</t>
+          <t>Ceylon Advanced Toastmasters Club</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>04</t>
         </is>
       </c>
       <c r="D23" s="6" t="n">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Ceylon Advanced Toastmasters Club</t>
+          <t>IAB Toastmasters Club</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D24" s="8" t="n">
@@ -1516,12 +1516,12 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Ansell Textiles Lanka Toastmasters Club</t>
+          <t>Wennappuwa Toastmasters Club</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D25" s="6" t="n">
@@ -1551,15 +1551,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1579,140 +1577,110 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-06-30  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:26  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Pathways Quality Award — Excellence (this Division)</t>
+          <t>Clubs Qualifying — Excellence (this Division)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>District Rank</t>
+          <t>Club</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Club</t>
+          <t>Area</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Area</t>
+          <t>Level 1</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Level 1</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
           <t>Level 3</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Ovation 2027</t>
-        </is>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
-        <v>16</v>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Ja-Ela Toastmasters Club</t>
+        </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Ja-Ela Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
           <t>H-03</t>
         </is>
       </c>
+      <c r="C7" s="6" t="n">
+        <v>8</v>
+      </c>
       <c r="D7" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="E7" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="n">
-        <v>25</v>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Negombo Toastmasters</t>
+        </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Negombo Toastmasters</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
           <t>H-02</t>
         </is>
       </c>
+      <c r="C8" s="8" t="n">
+        <v>4</v>
+      </c>
       <c r="D8" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E8" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
-        <v>30</v>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Silvermill Toastmasters Club</t>
+        </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Silvermill Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
           <t>H-02</t>
         </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>5</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E9" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="n">
-        <v>37</v>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Wattala Toastmasters Club</t>
+        </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Wattala Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
           <t>H-01</t>
         </is>
       </c>
+      <c r="C10" s="8" t="n">
+        <v>7</v>
+      </c>
       <c r="D10" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="E10" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F10" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1725,14 +1693,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1752,146 +1719,126 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-06-30  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:26  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Pathways Quality Award — Star (this Division)</t>
+          <t>Clubs Qualifying — Star (this Division)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>District Rank</t>
+          <t>Club</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Club</t>
+          <t>Area</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Area</t>
+          <t>Level 1</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Level 1</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
           <t>Level 3</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
-        <v>27</v>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Minuwangoda Toastmasters Club</t>
+        </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Minuwangoda Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
           <t>H-04</t>
         </is>
       </c>
+      <c r="C7" s="6" t="n">
+        <v>4</v>
+      </c>
       <c r="D7" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" s="6" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="n">
-        <v>31</v>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Omega Line</t>
+        </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Omega Line</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
           <t>H-02</t>
         </is>
       </c>
+      <c r="C8" s="8" t="n">
+        <v>8</v>
+      </c>
       <c r="D8" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="E8" s="8" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
-        <v>35</v>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Ragama Toastmasters Club</t>
+        </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Ragama Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
           <t>H-04</t>
         </is>
       </c>
+      <c r="C9" s="6" t="n">
+        <v>4</v>
+      </c>
       <c r="D9" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E9" s="6" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="n">
-        <v>39</v>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>SriLankan Airlines Toastmasters Club</t>
+        </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>SriLankan Airlines Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
           <t>H-04</t>
         </is>
       </c>
+      <c r="C10" s="8" t="n">
+        <v>4</v>
+      </c>
       <c r="D10" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E10" s="8" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
-        <v>40</v>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Star Garments Toastmasters Club</t>
+        </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Star Garments Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
           <t>H-03</t>
         </is>
       </c>
+      <c r="C11" s="6" t="n">
+        <v>4</v>
+      </c>
       <c r="D11" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E11" s="6" t="n">
         <v>2</v>
       </c>
     </row>

--- a/docs/exports/division/Division_H.xlsx
+++ b/docs/exports/division/Division_H.xlsx
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:26  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:41  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:26  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:41  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:26  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:41  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -917,7 +917,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:26  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:41  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1577,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:26  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:41  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1719,7 +1719,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:26  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:41  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/division/Division_H.xlsx
+++ b/docs/exports/division/Division_H.xlsx
@@ -515,14 +515,14 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:41  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:25  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Division H — Level Totals (District Rank #5 of 9)</t>
+          <t>Division H — Level Totals (District Rank #6 of 9)</t>
         </is>
       </c>
     </row>
@@ -555,19 +555,19 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>180</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -608,7 +608,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:41  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:25  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>8</v>
@@ -660,7 +660,7 @@
         <v>2</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -711,7 +711,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:41  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:25  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -774,22 +774,22 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>13</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -805,16 +805,16 @@
         <v>19</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E8" s="8" t="n">
         <v>3</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H8" s="8" t="n">
         <v>4</v>
@@ -858,19 +858,19 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F10" s="8" t="n">
         <v>8</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="H10" s="8" t="n">
         <v>4</v>
@@ -887,7 +887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -917,7 +917,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:41  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:25  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Negombo Toastmasters</t>
+          <t>Silvermill Toastmasters Club</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>4</v>
@@ -994,7 +994,7 @@
         <v>5</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>21</v>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Silvermill Toastmasters Club</t>
+          <t>Negombo Toastmasters</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -1015,19 +1015,19 @@
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E8" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -1036,25 +1036,25 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Ja-Ela Toastmasters Club</t>
+          <t>Wattala Toastmasters Club</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>3</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>18</v>
@@ -1066,28 +1066,28 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Wattala Toastmasters Club</t>
+          <t>Omega Line</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F10" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="G10" s="8" t="n">
-        <v>2</v>
-      </c>
       <c r="H10" s="8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
@@ -1096,16 +1096,16 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Omega Line</t>
+          <t>Minuwangoda Toastmasters Club</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>04</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>4</v>
@@ -1114,10 +1114,10 @@
         <v>2</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Minuwangoda Toastmasters Club</t>
+          <t>Ragama Toastmasters Club</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Ragama Toastmasters Club</t>
+          <t>SriLankan Airlines Toastmasters Club</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1186,28 +1186,28 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>SriLankan Airlines Toastmasters Club</t>
+          <t>Ja-Ela Toastmasters Club</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -1228,7 +1228,7 @@
         <v>4</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>2</v>
@@ -1237,7 +1237,7 @@
         <v>2</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
@@ -1246,28 +1246,28 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Wayamba Toastmasters</t>
+          <t>United Tractors Toastmasters Club</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>United Tractors Toastmasters Club</t>
+          <t>Negombo Speakers Forum</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -1285,19 +1285,19 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -1306,28 +1306,28 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Negombo Speakers Forum</t>
+          <t>Wayamba Toastmasters</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -1354,10 +1354,10 @@
         <v>0</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -1507,36 +1507,6 @@
         <v>0</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>Wennappuwa Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1577,7 +1547,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:41  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:25  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1613,25 +1583,25 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Ja-Ela Toastmasters Club</t>
+          <t>Negombo Toastmasters</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Negombo Toastmasters</t>
+          <t>Silvermill Toastmasters Club</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -1640,7 +1610,7 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" s="8" t="n">
         <v>5</v>
@@ -1649,34 +1619,34 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Silvermill Toastmasters Club</t>
+          <t>Wattala Toastmasters Club</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Wattala Toastmasters Club</t>
+          <t>Ja-Ela Toastmasters Club</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" s="8" t="n">
         <v>3</v>
@@ -1719,7 +1689,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 01 Jul 2026, 17:41  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:25  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/division/Division_H.xlsx
+++ b/docs/exports/division/Division_H.xlsx
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:30  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:30  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:30  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -917,7 +917,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:30  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1547,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:30  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:30  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/division/Division_H.xlsx
+++ b/docs/exports/division/Division_H.xlsx
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:30  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-05-24  |  Report generated 02 Jul 2026, 16:21  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -555,7 +555,7 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B7" s="6" t="n">
         <v>39</v>
@@ -567,7 +567,7 @@
         <v>39</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -608,7 +608,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:30  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-05-24  |  Report generated 02 Jul 2026, 16:21  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
         <v>8</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>2</v>
@@ -711,7 +711,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:30  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-05-24  |  Report generated 02 Jul 2026, 16:21  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D8" s="8" t="n">
         <v>11</v>
@@ -814,7 +814,7 @@
         <v>4</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H8" s="8" t="n">
         <v>4</v>
@@ -917,7 +917,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:30  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-05-24  |  Report generated 02 Jul 2026, 16:21  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>United Tractors Toastmasters Club</t>
+          <t>Negombo Speakers Forum</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E16" s="8" t="n">
         <v>2</v>
@@ -1264,10 +1264,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Negombo Speakers Forum</t>
+          <t>United Tractors Toastmasters Club</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E17" s="6" t="n">
         <v>2</v>
@@ -1294,7 +1294,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" s="6" t="n">
         <v>7</v>
@@ -1547,7 +1547,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:30  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-05-24  |  Report generated 02 Jul 2026, 16:21  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 15:30  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-05-24  |  Report generated 02 Jul 2026, 16:21  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/division/Division_H.xlsx
+++ b/docs/exports/division/Division_H.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Division H — Level Totals (D" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="District-Wide Standing — Ran" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Area Leaderboard (within Div" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Club Leaderboard (within Div" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Clubs Qualifying — Excellenc" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Clubs Qualifying — Star (thi" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Division H — Level Totals (D" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="District-Wide Standing — Ran" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Area Leaderboard (within Div" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Club Leaderboard (within Div" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clubs Qualifying — Excellenc" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clubs Qualifying — Star (thi" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -515,14 +515,14 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-05-24  |  Report generated 02 Jul 2026, 16:21  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:25  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Division H — Level Totals (District Rank #6 of 9)</t>
+          <t>Division H — Level Totals (District Rank #5 of 9)</t>
         </is>
       </c>
     </row>
@@ -555,19 +555,19 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>161</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -608,7 +608,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-05-24  |  Report generated 02 Jul 2026, 16:21  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:25  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -651,16 +651,16 @@
         <v>7</v>
       </c>
       <c r="B7" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C7" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="C7" s="6" t="n">
-        <v>7</v>
-      </c>
       <c r="D7" s="6" t="n">
         <v>2</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -711,7 +711,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-05-24  |  Report generated 02 Jul 2026, 16:21  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:25  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -774,22 +774,22 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>13</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -802,19 +802,19 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E8" s="8" t="n">
         <v>3</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H8" s="8" t="n">
         <v>4</v>
@@ -858,19 +858,19 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F10" s="8" t="n">
         <v>8</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="H10" s="8" t="n">
         <v>4</v>
@@ -887,7 +887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -917,7 +917,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-05-24  |  Report generated 02 Jul 2026, 16:21  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:25  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Silvermill Toastmasters Club</t>
+          <t>Negombo Toastmasters</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>4</v>
@@ -994,7 +994,7 @@
         <v>5</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>21</v>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Negombo Toastmasters</t>
+          <t>Silvermill Toastmasters Club</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -1015,19 +1015,19 @@
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
@@ -1036,25 +1036,25 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Wattala Toastmasters Club</t>
+          <t>Ja-Ela Toastmasters Club</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>3</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>18</v>
@@ -1066,28 +1066,28 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Omega Line</t>
+          <t>Wattala Toastmasters Club</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
@@ -1096,16 +1096,16 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Minuwangoda Toastmasters Club</t>
+          <t>Omega Line</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>4</v>
@@ -1114,10 +1114,10 @@
         <v>2</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Ragama Toastmasters Club</t>
+          <t>Minuwangoda Toastmasters Club</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>SriLankan Airlines Toastmasters Club</t>
+          <t>Ragama Toastmasters Club</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1186,28 +1186,28 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Ja-Ela Toastmasters Club</t>
+          <t>SriLankan Airlines Toastmasters Club</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -1228,7 +1228,7 @@
         <v>4</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>2</v>
@@ -1237,7 +1237,7 @@
         <v>2</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
@@ -1246,28 +1246,28 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Negombo Speakers Forum</t>
+          <t>Wayamba Toastmasters</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1306,28 +1306,28 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Wayamba Toastmasters</t>
+          <t>Negombo Speakers Forum</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E18" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F18" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="8" t="n">
-        <v>3</v>
-      </c>
       <c r="H18" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -1354,10 +1354,10 @@
         <v>0</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1507,6 +1507,36 @@
         <v>0</v>
       </c>
       <c r="H24" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Wennappuwa Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1547,7 +1577,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-05-24  |  Report generated 02 Jul 2026, 16:21  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:25  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1583,25 +1613,25 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Negombo Toastmasters</t>
+          <t>Ja-Ela Toastmasters Club</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Silvermill Toastmasters Club</t>
+          <t>Negombo Toastmasters</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -1610,7 +1640,7 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D8" s="8" t="n">
         <v>5</v>
@@ -1619,34 +1649,34 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Wattala Toastmasters Club</t>
+          <t>Silvermill Toastmasters Club</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Ja-Ela Toastmasters Club</t>
+          <t>Wattala Toastmasters Club</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D10" s="8" t="n">
         <v>3</v>
@@ -1689,7 +1719,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-05-24  |  Report generated 02 Jul 2026, 16:21  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:25  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/division/Division_H.xlsx
+++ b/docs/exports/division/Division_H.xlsx
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:37  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:37  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:37  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -917,7 +917,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:37  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1577,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:37  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1719,7 +1719,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:37  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/division/Division_H.xlsx
+++ b/docs/exports/division/Division_H.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Division H — Level Totals (D" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="District-Wide Standing — Ran" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Area Leaderboard (within Div" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Club Leaderboard (within Div" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clubs Qualifying — Excellenc" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clubs Qualifying — Star (thi" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Division H — Level Totals (D" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="District-Wide Standing — Ran" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Area Leaderboard (within Div" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Club Leaderboard (within Div" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Clubs Qualifying — Excellenc" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Clubs Qualifying — Star (thi" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -515,14 +515,14 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:37  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-05-09  |  Report generated 02 Jul 2026, 18:38  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Division H — Level Totals (District Rank #5 of 9)</t>
+          <t>Division H — Level Totals (District Rank #6 of 9)</t>
         </is>
       </c>
     </row>
@@ -555,19 +555,19 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>180</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -608,7 +608,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:37  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-05-09  |  Report generated 02 Jul 2026, 18:38  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>8</v>
@@ -660,7 +660,7 @@
         <v>2</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -711,7 +711,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:37  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-05-09  |  Report generated 02 Jul 2026, 18:38  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -774,22 +774,22 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>13</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -798,26 +798,26 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Area 01</t>
+          <t>Area 04</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F8" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="H8" s="8" t="n">
         <v>5</v>
-      </c>
-      <c r="G8" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="H8" s="8" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -826,26 +826,26 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Area 04</t>
+          <t>Area 01</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -858,19 +858,19 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F10" s="8" t="n">
         <v>8</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="H10" s="8" t="n">
         <v>4</v>
@@ -887,7 +887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -917,7 +917,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:37  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-05-09  |  Report generated 02 Jul 2026, 18:38  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Negombo Toastmasters</t>
+          <t>Silvermill Toastmasters Club</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>4</v>
@@ -994,10 +994,10 @@
         <v>5</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Silvermill Toastmasters Club</t>
+          <t>Negombo Toastmasters</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -1015,19 +1015,19 @@
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E8" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
@@ -1036,25 +1036,25 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Ja-Ela Toastmasters Club</t>
+          <t>Wattala Toastmasters Club</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>3</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>18</v>
@@ -1066,28 +1066,28 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Wattala Toastmasters Club</t>
+          <t>Omega Line</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
         <v>7</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F10" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="G10" s="8" t="n">
-        <v>2</v>
-      </c>
       <c r="H10" s="8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -1096,16 +1096,16 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Omega Line</t>
+          <t>Minuwangoda Toastmasters Club</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>04</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>4</v>
@@ -1114,10 +1114,10 @@
         <v>2</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Minuwangoda Toastmasters Club</t>
+          <t>Ragama Toastmasters Club</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Ragama Toastmasters Club</t>
+          <t>SriLankan Airlines Toastmasters Club</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1186,19 +1186,19 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>SriLankan Airlines Toastmasters Club</t>
+          <t>Star Garments Toastmasters Club</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
         <v>4</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F14" s="8" t="n">
         <v>2</v>
@@ -1207,7 +1207,7 @@
         <v>2</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -1216,28 +1216,28 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Star Garments Toastmasters Club</t>
+          <t>Negombo Speakers Forum</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
         <v>4</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -1246,16 +1246,16 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Wayamba Toastmasters</t>
+          <t>Ja-Ela Toastmasters Club</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E16" s="8" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H16" s="8" t="n">
         <v>5</v>
-      </c>
-      <c r="H16" s="8" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="17">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -1306,28 +1306,28 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Negombo Speakers Forum</t>
+          <t>Wayamba Toastmasters</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -1336,28 +1336,28 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Sunday Live Speakers Forum</t>
+          <t>Ampara Toastmasters Club</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="G19" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1366,25 +1366,25 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Ampara Toastmasters Club</t>
+          <t>Sunday Live Speakers Forum</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="8" t="n">
         <v>1</v>
-      </c>
-      <c r="G20" s="8" t="n">
-        <v>2</v>
       </c>
       <c r="H20" s="8" t="n">
         <v>3</v>
@@ -1507,36 +1507,6 @@
         <v>0</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>Wennappuwa Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1577,7 +1547,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:37  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-05-09  |  Report generated 02 Jul 2026, 18:38  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1613,25 +1583,25 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Ja-Ela Toastmasters Club</t>
+          <t>Negombo Toastmasters</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>H-03</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Negombo Toastmasters</t>
+          <t>Silvermill Toastmasters Club</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -1640,7 +1610,7 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" s="8" t="n">
         <v>5</v>
@@ -1649,34 +1619,34 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Silvermill Toastmasters Club</t>
+          <t>Wattala Toastmasters Club</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Wattala Toastmasters Club</t>
+          <t>Ja-Ela Toastmasters Club</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>H-03</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" s="8" t="n">
         <v>3</v>
@@ -1719,7 +1689,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 02 Jul 2026, 12:37  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-05-09  |  Report generated 02 Jul 2026, 18:38  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/division/Division_H.xlsx
+++ b/docs/exports/division/Division_H.xlsx
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-05-09  |  Report generated 02 Jul 2026, 18:38  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 18:44  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -555,19 +555,19 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>148</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -608,7 +608,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-05-09  |  Report generated 02 Jul 2026, 18:38  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 18:44  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-05-09  |  Report generated 02 Jul 2026, 18:38  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 18:44  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -774,19 +774,19 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>13</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>5</v>
@@ -798,26 +798,26 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Area 04</t>
+          <t>Area 01</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -826,26 +826,26 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Area 01</t>
+          <t>Area 04</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -858,19 +858,19 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D10" s="8" t="n">
         <v>3</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" s="8" t="n">
         <v>8</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H10" s="8" t="n">
         <v>4</v>
@@ -917,7 +917,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-05-09  |  Report generated 02 Jul 2026, 18:38  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 18:44  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -994,10 +994,10 @@
         <v>5</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
@@ -1021,13 +1021,13 @@
         <v>4</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G8" s="8" t="n">
         <v>8</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" s="8" t="n">
         <v>4</v>
@@ -1087,7 +1087,7 @@
         <v>3</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Star Garments Toastmasters Club</t>
+          <t>Ja-Ela Toastmasters Club</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -1195,19 +1195,19 @@
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Negombo Speakers Forum</t>
+          <t>Star Garments Toastmasters Club</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
@@ -1231,13 +1231,13 @@
         <v>2</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
@@ -1246,28 +1246,28 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Ja-Ela Toastmasters Club</t>
+          <t>United Tractors Toastmasters Club</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>United Tractors Toastmasters Club</t>
+          <t>Negombo Speakers Forum</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -1288,16 +1288,16 @@
         <v>4</v>
       </c>
       <c r="E17" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="H17" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="8" t="n">
         <v>1</v>
@@ -1327,7 +1327,7 @@
         <v>3</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -1336,28 +1336,28 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Ampara Toastmasters Club</t>
+          <t>Sunday Live Speakers Forum</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="6" t="n">
-        <v>2</v>
-      </c>
       <c r="H19" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -1366,25 +1366,25 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Sunday Live Speakers Forum</t>
+          <t>Ampara Toastmasters Club</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="E20" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="G20" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="8" t="n">
         <v>3</v>
@@ -1547,7 +1547,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-05-09  |  Report generated 02 Jul 2026, 18:38  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 18:44  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-05-09  |  Report generated 02 Jul 2026, 18:38  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 18:44  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/division/Division_H.xlsx
+++ b/docs/exports/division/Division_H.xlsx
@@ -515,14 +515,14 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 18:44  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:51  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Division H — Level Totals (District Rank #6 of 9)</t>
+          <t>Division H — Level Totals (District Rank #5 of 9)</t>
         </is>
       </c>
     </row>
@@ -555,19 +555,19 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>162</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -608,7 +608,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 18:44  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:51  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -648,19 +648,19 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>2</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -711,7 +711,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 18:44  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:51  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -774,19 +774,19 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>5</v>
@@ -802,19 +802,19 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F8" s="8" t="n">
-        <v>4</v>
-      </c>
       <c r="G8" s="8" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="H8" s="8" t="n">
         <v>4</v>
@@ -830,22 +830,22 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -858,22 +858,22 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D10" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H10" s="8" t="n">
         <v>3</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F10" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="G10" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="H10" s="8" t="n">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -887,11 +887,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -917,7 +917,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 18:44  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:51  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -988,16 +988,16 @@
         <v>5</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>5</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Negombo Toastmasters</t>
+          <t>Omega Line</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -1015,19 +1015,19 @@
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -1045,19 +1045,19 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Omega Line</t>
+          <t>Negombo Toastmasters</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F10" s="8" t="n">
         <v>2</v>
@@ -1087,7 +1087,7 @@
         <v>3</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Minuwangoda Toastmasters Club</t>
+          <t>Ragama Toastmasters Club</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -1105,19 +1105,19 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>2</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -1126,28 +1126,28 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Ragama Toastmasters Club</t>
+          <t>Ja-Ela Toastmasters Club</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1156,28 +1156,28 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>SriLankan Airlines Toastmasters Club</t>
+          <t>Negombo Speakers Forum</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1186,28 +1186,28 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Ja-Ela Toastmasters Club</t>
+          <t>SriLankan Airlines Toastmasters Club</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="8" t="n">
         <v>3</v>
-      </c>
-      <c r="H14" s="8" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -1216,28 +1216,28 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Star Garments Toastmasters Club</t>
+          <t>Wayamba Toastmasters</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>2</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1246,28 +1246,28 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>United Tractors Toastmasters Club</t>
+          <t>Star Garments Toastmasters Club</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Negombo Speakers Forum</t>
+          <t>Sunday Live Speakers Forum</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1306,28 +1306,28 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Wayamba Toastmasters</t>
+          <t>United Tractors Toastmasters Club</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1336,19 +1336,19 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Sunday Live Speakers Forum</t>
+          <t>FTZ Toastmasters Club</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>1</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1366,12 +1366,12 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Ampara Toastmasters Club</t>
+          <t>Minuwangoda Toastmasters Club</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
@@ -1381,13 +1381,13 @@
         <v>0</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1396,12 +1396,12 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>FTZ Toastmasters Club</t>
+          <t>Ceylon Advanced Toastmasters Club</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="D21" s="6" t="n">
@@ -1414,10 +1414,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1426,12 +1426,12 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Ansell Textiles Lanka Toastmasters Club</t>
+          <t>IAB Toastmasters Club</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -1447,66 +1447,6 @@
         <v>0</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>Ceylon Advanced Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>IAB Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1547,7 +1487,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 18:44  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:51  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1523,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Negombo Toastmasters</t>
+          <t>Silvermill Toastmasters Club</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -1592,7 +1532,7 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>5</v>
@@ -1601,7 +1541,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Silvermill Toastmasters Club</t>
+          <t>Negombo Toastmasters</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -1610,7 +1550,7 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D8" s="8" t="n">
         <v>5</v>
@@ -1689,7 +1629,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-05  |  Report generated 02 Jul 2026, 18:44  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:51  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/division/Division_H.xlsx
+++ b/docs/exports/division/Division_H.xlsx
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:51  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:51  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:51  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -917,7 +917,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:51  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:51  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:51  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/division/Division_H.xlsx
+++ b/docs/exports/division/Division_H.xlsx
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -917,7 +917,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 18:55  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/division/Division_H.xlsx
+++ b/docs/exports/division/Division_H.xlsx
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -917,7 +917,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -1487,7 +1487,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1536,60 +1536,6 @@
       </c>
       <c r="D7" s="6" t="n">
         <v>5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Negombo Toastmasters</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>H-02</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Wattala Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>H-01</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Ja-Ela Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>H-03</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1603,10 +1549,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -1629,7 +1575,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:02  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1665,92 +1611,12 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Minuwangoda Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>H-04</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Omega Line</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>H-02</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Ragama Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>H-04</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>SriLankan Airlines Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>H-04</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D10" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Star Garments Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>H-03</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>2</v>
-      </c>
+          <t>No clubs yet</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/exports/division/Division_H.xlsx
+++ b/docs/exports/division/Division_H.xlsx
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -555,19 +555,19 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>72</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -608,7 +608,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -654,10 +654,10 @@
         <v>5</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>5</v>
@@ -711,7 +711,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -774,19 +774,19 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>8</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>5</v>
@@ -798,23 +798,23 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Area 01</t>
+          <t>Area 04</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E8" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="H8" s="8" t="n">
         <v>4</v>
@@ -826,26 +826,26 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Area 04</t>
+          <t>Area 03</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" s="6" t="n">
         <v>3</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -854,26 +854,26 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Area 03</t>
+          <t>Area 01</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G10" s="8" t="n">
-        <v>6</v>
-      </c>
       <c r="H10" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -917,7 +917,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -994,10 +994,10 @@
         <v>5</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -1015,19 +1015,19 @@
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="8" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -1036,28 +1036,28 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Wattala Toastmasters Club</t>
+          <t>Negombo Toastmasters</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -1066,28 +1066,28 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Negombo Toastmasters</t>
+          <t>Ragama Toastmasters Club</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>04</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -1096,28 +1096,28 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Ragama Toastmasters Club</t>
+          <t>Wattala Toastmasters Club</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="E11" s="6" t="n">
-        <v>1</v>
-      </c>
       <c r="F11" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -1156,19 +1156,19 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Negombo Speakers Forum</t>
+          <t>SriLankan Airlines Toastmasters Club</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="6" t="n">
         <v>2</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>0</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>0</v>
@@ -1186,25 +1186,25 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>SriLankan Airlines Toastmasters Club</t>
+          <t>Wayamba Toastmasters</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="8" t="n">
         <v>2</v>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>1</v>
       </c>
       <c r="H14" s="8" t="n">
         <v>3</v>
@@ -1216,28 +1216,28 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Wayamba Toastmasters</t>
+          <t>Star Garments Toastmasters Club</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="6" t="n">
         <v>2</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Star Garments Toastmasters Club</t>
+          <t>FTZ Toastmasters Club</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -1258,7 +1258,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="8" t="n">
         <v>0</v>
@@ -1267,7 +1267,7 @@
         <v>1</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1306,16 +1306,16 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>United Tractors Toastmasters Club</t>
+          <t>Ceylon Advanced Toastmasters Club</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E18" s="8" t="n">
         <v>0</v>
@@ -1327,7 +1327,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>FTZ Toastmasters Club</t>
+          <t>IAB Toastmasters Club</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
@@ -1354,10 +1354,10 @@
         <v>0</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1384,10 +1384,10 @@
         <v>0</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1396,12 +1396,12 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Ceylon Advanced Toastmasters Club</t>
+          <t>Negombo Speakers Forum</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D21" s="6" t="n">
@@ -1426,12 +1426,12 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>IAB Toastmasters Club</t>
+          <t>United Tractors Toastmasters Club</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -1487,7 +1487,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-12-31  |  Report generated 02 Jul 2026, 19:27  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/division/Division_H.xlsx
+++ b/docs/exports/division/Division_H.xlsx
@@ -515,14 +515,14 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 19:50  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Division H — Level Totals (District Rank #5 of 9)</t>
+          <t>Division H — Level Totals (District Rank #6 of 9)</t>
         </is>
       </c>
     </row>
@@ -555,19 +555,19 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>46</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -608,7 +608,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 19:50  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -648,19 +648,19 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="6" t="n">
         <v>6</v>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -711,7 +711,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 19:50  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -774,19 +774,19 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>5</v>
@@ -802,19 +802,19 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="H8" s="8" t="n">
         <v>4</v>
@@ -826,26 +826,26 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Area 03</t>
+          <t>Area 01</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -854,23 +854,23 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Area 01</t>
+          <t>Area 03</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="H10" s="8" t="n">
         <v>4</v>
@@ -887,11 +887,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -917,7 +917,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 19:50  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -988,16 +988,16 @@
         <v>5</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>5</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Omega Line</t>
+          <t>Negombo Toastmasters</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -1015,19 +1015,19 @@
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
@@ -1036,28 +1036,28 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Negombo Toastmasters</t>
+          <t>Wattala Toastmasters Club</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
@@ -1066,28 +1066,28 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Ragama Toastmasters Club</t>
+          <t>Omega Line</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -1096,28 +1096,28 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Wattala Toastmasters Club</t>
+          <t>Ragama Toastmasters Club</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -1126,28 +1126,28 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Ja-Ela Toastmasters Club</t>
+          <t>SriLankan Airlines Toastmasters Club</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>SriLankan Airlines Toastmasters Club</t>
+          <t>Minuwangoda Toastmasters Club</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>1</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
@@ -1186,28 +1186,28 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Wayamba Toastmasters</t>
+          <t>Star Garments Toastmasters Club</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G14" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -1216,19 +1216,19 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Star Garments Toastmasters Club</t>
+          <t>Negombo Speakers Forum</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>0</v>
@@ -1237,7 +1237,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>FTZ Toastmasters Club</t>
+          <t>Ja-Ela Toastmasters Club</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -1255,19 +1255,19 @@
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Sunday Live Speakers Forum</t>
+          <t>United Tractors Toastmasters Club</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -1285,19 +1285,19 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -1306,28 +1306,28 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Ceylon Advanced Toastmasters Club</t>
+          <t>Wayamba Toastmasters</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>IAB Toastmasters Club</t>
+          <t>Ampara Toastmasters Club</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
@@ -1351,13 +1351,13 @@
         <v>0</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1366,28 +1366,28 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Minuwangoda Toastmasters Club</t>
+          <t>Sunday Live Speakers Forum</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1396,12 +1396,12 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Negombo Speakers Forum</t>
+          <t>FTZ Toastmasters Club</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D21" s="6" t="n">
@@ -1414,10 +1414,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1426,12 +1426,12 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>United Tractors Toastmasters Club</t>
+          <t>Ansell Textiles Lanka Toastmasters Club</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="D22" s="8" t="n">
@@ -1447,6 +1447,36 @@
         <v>0</v>
       </c>
       <c r="H22" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>IAB Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1461,7 +1491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -1487,7 +1517,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 19:50  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1536,6 +1566,42 @@
       </c>
       <c r="D7" s="6" t="n">
         <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Negombo Toastmasters</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>H-02</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Wattala Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>H-01</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1549,10 +1615,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="39" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -1575,7 +1641,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2025-10-31  |  Report generated 02 Jul 2026, 19:37  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 19:50  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1611,12 +1677,92 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>No clubs yet</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr"/>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
+          <t>Minuwangoda Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>H-04</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Omega Line</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>H-02</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Ragama Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>H-04</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>SriLankan Airlines Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>H-04</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Star Garments Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>H-03</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/exports/division/Division_H.xlsx
+++ b/docs/exports/division/Division_H.xlsx
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 19:50  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 20:06  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 19:50  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 20:06  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 19:50  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 20:06  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -917,7 +917,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 19:50  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 20:06  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1517,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 19:50  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 20:06  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 19:50  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 20:06  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/division/Division_H.xlsx
+++ b/docs/exports/division/Division_H.xlsx
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 20:06  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-03-05  |  Report generated 02 Jul 2026, 20:33  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -555,19 +555,19 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>147</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -608,7 +608,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 20:06  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-03-05  |  Report generated 02 Jul 2026, 20:33  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>2</v>
@@ -711,7 +711,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 20:06  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-03-05  |  Report generated 02 Jul 2026, 20:33  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -774,19 +774,19 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>10</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>5</v>
@@ -798,23 +798,23 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Area 04</t>
+          <t>Area 01</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
         <v>12</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H8" s="8" t="n">
         <v>4</v>
@@ -826,14 +826,14 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Area 01</t>
+          <t>Area 04</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>3</v>
@@ -842,10 +842,10 @@
         <v>4</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -858,19 +858,19 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H10" s="8" t="n">
         <v>4</v>
@@ -887,7 +887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -917,7 +917,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 20:06  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-03-05  |  Report generated 02 Jul 2026, 20:33  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -994,10 +994,10 @@
         <v>5</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Negombo Toastmasters</t>
+          <t>Omega Line</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -1015,19 +1015,19 @@
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E8" s="8" t="n">
         <v>4</v>
       </c>
       <c r="F8" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="G8" s="8" t="n">
-        <v>8</v>
-      </c>
       <c r="H8" s="8" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -1036,28 +1036,28 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Wattala Toastmasters Club</t>
+          <t>Negombo Toastmasters</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>3</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
@@ -1066,28 +1066,28 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Omega Line</t>
+          <t>Wattala Toastmasters Club</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F10" s="8" t="n">
         <v>2</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -1108,7 +1108,7 @@
         <v>4</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>2</v>
@@ -1117,7 +1117,7 @@
         <v>2</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
@@ -1135,19 +1135,19 @@
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -1156,28 +1156,28 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Minuwangoda Toastmasters Club</t>
+          <t>Ja-Ela Toastmasters Club</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -1186,28 +1186,28 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Star Garments Toastmasters Club</t>
+          <t>Negombo Speakers Forum</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -1216,19 +1216,19 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Negombo Speakers Forum</t>
+          <t>Star Garments Toastmasters Club</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>0</v>
@@ -1237,7 +1237,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1246,28 +1246,28 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Ja-Ela Toastmasters Club</t>
+          <t>United Tractors Toastmasters Club</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="8" t="n">
         <v>3</v>
-      </c>
-      <c r="H16" s="8" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -1276,28 +1276,28 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>United Tractors Toastmasters Club</t>
+          <t>Wayamba Toastmasters</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1306,28 +1306,28 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Wayamba Toastmasters</t>
+          <t>Ampara Toastmasters Club</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1336,28 +1336,28 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Ampara Toastmasters Club</t>
+          <t>Sunday Live Speakers Forum</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1366,19 +1366,19 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Sunday Live Speakers Forum</t>
+          <t>FTZ Toastmasters Club</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" s="8" t="n">
         <v>0</v>
@@ -1387,7 +1387,7 @@
         <v>1</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1396,12 +1396,12 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>FTZ Toastmasters Club</t>
+          <t>Minuwangoda Toastmasters Club</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="D21" s="6" t="n">
@@ -1456,27 +1456,57 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
+          <t>Ceylon Advanced Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
           <t>IAB Toastmasters Club</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="6" t="n">
+      <c r="D24" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1491,7 +1521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -1517,7 +1547,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 20:06  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-03-05  |  Report generated 02 Jul 2026, 20:33  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1566,42 +1596,6 @@
       </c>
       <c r="D7" s="6" t="n">
         <v>5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Negombo Toastmasters</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>H-02</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Wattala Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>H-01</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1615,10 +1609,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -1641,7 +1635,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-04-30  |  Report generated 02 Jul 2026, 20:06  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-03-05  |  Report generated 02 Jul 2026, 20:33  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1677,19 +1671,19 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Minuwangoda Toastmasters Club</t>
+          <t>Negombo Toastmasters</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>H-02</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -1731,36 +1725,18 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>SriLankan Airlines Toastmasters Club</t>
+          <t>Wattala Toastmasters Club</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>H-04</t>
+          <t>H-01</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Star Garments Toastmasters Club</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>H-03</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D11" s="6" t="n">
         <v>2</v>
       </c>
     </row>

--- a/docs/exports/division/Division_H.xlsx
+++ b/docs/exports/division/Division_H.xlsx
@@ -515,14 +515,14 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-03-05  |  Report generated 02 Jul 2026, 20:33  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:03  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Division H — Level Totals (District Rank #6 of 9)</t>
+          <t>Division H — Level Totals (District Rank #5 of 9)</t>
         </is>
       </c>
     </row>
@@ -555,19 +555,19 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>107</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -608,7 +608,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-03-05  |  Report generated 02 Jul 2026, 20:33  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:03  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -654,13 +654,13 @@
         <v>7</v>
       </c>
       <c r="C7" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="6" t="n">
         <v>5</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -711,7 +711,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-03-05  |  Report generated 02 Jul 2026, 20:33  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:03  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -774,22 +774,22 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -802,19 +802,19 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="H8" s="8" t="n">
         <v>4</v>
@@ -830,19 +830,19 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="E9" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="D9" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>3</v>
-      </c>
       <c r="F9" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>5</v>
@@ -858,19 +858,19 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="H10" s="8" t="n">
         <v>4</v>
@@ -887,7 +887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -917,7 +917,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-03-05  |  Report generated 02 Jul 2026, 20:33  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:03  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Silvermill Toastmasters Club</t>
+          <t>Negombo Toastmasters</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>4</v>
@@ -994,10 +994,10 @@
         <v>5</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Omega Line</t>
+          <t>Silvermill Toastmasters Club</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -1015,19 +1015,19 @@
         </is>
       </c>
       <c r="D8" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="E8" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F8" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" s="8" t="n">
-        <v>3</v>
-      </c>
       <c r="H8" s="8" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
@@ -1036,28 +1036,28 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Negombo Toastmasters</t>
+          <t>Ja-Ela Toastmasters Club</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>3</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
@@ -1075,19 +1075,19 @@
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" s="8" t="n">
         <v>6</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
@@ -1096,28 +1096,28 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Ragama Toastmasters Club</t>
+          <t>Omega Line</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E11" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F11" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>2</v>
-      </c>
       <c r="H11" s="6" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>SriLankan Airlines Toastmasters Club</t>
+          <t>Minuwangoda Toastmasters Club</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -1135,19 +1135,19 @@
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -1156,28 +1156,28 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Ja-Ela Toastmasters Club</t>
+          <t>Ragama Toastmasters Club</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
@@ -1186,28 +1186,28 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Negombo Speakers Forum</t>
+          <t>SriLankan Airlines Toastmasters Club</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -1225,19 +1225,19 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
@@ -1246,28 +1246,28 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>United Tractors Toastmasters Club</t>
+          <t>Wayamba Toastmasters</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
@@ -1276,28 +1276,28 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Wayamba Toastmasters</t>
+          <t>United Tractors Toastmasters Club</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1306,28 +1306,28 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Ampara Toastmasters Club</t>
+          <t>Negombo Speakers Forum</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E19" s="6" t="n">
         <v>1</v>
@@ -1354,10 +1354,10 @@
         <v>0</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>FTZ Toastmasters Club</t>
+          <t>Ampara Toastmasters Club</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -1381,13 +1381,13 @@
         <v>0</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1396,12 +1396,12 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Minuwangoda Toastmasters Club</t>
+          <t>FTZ Toastmasters Club</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D21" s="6" t="n">
@@ -1507,6 +1507,36 @@
         <v>0</v>
       </c>
       <c r="H24" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Wennappuwa Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1521,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -1547,7 +1577,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-03-05  |  Report generated 02 Jul 2026, 20:33  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:03  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1596,6 +1626,60 @@
       </c>
       <c r="D7" s="6" t="n">
         <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Negombo Toastmasters</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>H-02</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Wattala Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>H-01</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Ja-Ela Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>H-03</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1609,10 +1693,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="39" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -1635,7 +1719,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-03-05  |  Report generated 02 Jul 2026, 20:33  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:03  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1755,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Negombo Toastmasters</t>
+          <t>Omega Line</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -1680,25 +1764,25 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Omega Line</t>
+          <t>Ragama Toastmasters Club</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>H-02</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D8" s="8" t="n">
         <v>2</v>
@@ -1707,7 +1791,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Ragama Toastmasters Club</t>
+          <t>Minuwangoda Toastmasters Club</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -1725,18 +1809,36 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Wattala Toastmasters Club</t>
+          <t>SriLankan Airlines Toastmasters Club</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>H-01</t>
+          <t>H-04</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D10" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Star Garments Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>H-03</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" s="6" t="n">
         <v>2</v>
       </c>
     </row>

--- a/docs/exports/division/Division_H.xlsx
+++ b/docs/exports/division/Division_H.xlsx
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:03  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:24  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:03  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:24  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:03  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:24  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -917,7 +917,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:03  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:24  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1577,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:03  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:24  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -1719,7 +1719,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:03  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:24  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
